--- a/conference_registration_forms/022_innovative_pedagogy_symposium_registration--conference_registration_forms.xlsx
+++ b/conference_registration_forms/022_innovative_pedagogy_symposium_registration--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -912,46 +912,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>session_interests_choices</t>
+          <t>accessibility_needs_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>session_interests_choices</t>
+          <t>accessibility_needs_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -963,46 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>accessibility_needs_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>accessibility_needs_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
